--- a/results/table.xlsx
+++ b/results/table.xlsx
@@ -7,15 +7,14 @@
     <workbookView windowWidth="30720" windowHeight="15540"/>
   </bookViews>
   <sheets>
-    <sheet name="overall" sheetId="7" r:id="rId1"/>
-    <sheet name="test_domain_k" sheetId="1" r:id="rId2"/>
-    <sheet name="test_domain_oc" sheetId="2" r:id="rId3"/>
-    <sheet name="od_num_oc" sheetId="3" r:id="rId4"/>
-    <sheet name="od_num_k" sheetId="4" r:id="rId5"/>
-    <sheet name="od_num_s" sheetId="5" r:id="rId6"/>
+    <sheet name="overall" sheetId="1" r:id="rId1"/>
+    <sheet name="test_domain_k" sheetId="2" r:id="rId2"/>
+    <sheet name="test_domain_oc" sheetId="3" r:id="rId3"/>
+    <sheet name="test_domain_s" sheetId="9" r:id="rId4"/>
+    <sheet name="od_num" sheetId="4" r:id="rId5"/>
+    <sheet name="data_size" sheetId="7" r:id="rId6"/>
     <sheet name="RAPL" sheetId="6" r:id="rId7"/>
-    <sheet name="data_size" sheetId="8" r:id="rId8"/>
-    <sheet name="abolation" sheetId="9" r:id="rId9"/>
+    <sheet name="abolation" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,8 +33,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="47">
   <si>
     <t>layer</t>
   </si>
@@ -76,6 +97,9 @@
     <t>Fout</t>
   </si>
   <si>
+    <t>weighted average</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
@@ -100,7 +124,14 @@
     <t>Diff</t>
   </si>
   <si>
-    <t>源域数量</t>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Src Domains</t>
+  </si>
+  <si>
+    <t>Regression
+(Acc of Cout)</t>
   </si>
   <si>
     <t>1</t>
@@ -109,46 +140,47 @@
     <t>2</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
+    <t>Classification
+(F1 of S)</t>
+  </si>
+  <si>
+    <t>Data Ratio</t>
+  </si>
+  <si>
+    <t>ours</t>
+  </si>
+  <si>
+    <t>baseline</t>
+  </si>
+  <si>
+    <t>diff</t>
+  </si>
+  <si>
     <t>RAPL Domain</t>
   </si>
   <si>
+    <t>PP0</t>
+  </si>
+  <si>
+    <t>DRAM</t>
+  </si>
+  <si>
+    <t>PP0+DRAM</t>
+  </si>
+  <si>
+    <t>回归模型</t>
+  </si>
+  <si>
+    <t>分类模型</t>
+  </si>
+  <si>
     <t>Acc of Oc</t>
   </si>
   <si>
-    <t>F1 of K</t>
-  </si>
-  <si>
-    <t>PP0</t>
-  </si>
-  <si>
-    <t>DRAM</t>
-  </si>
-  <si>
-    <t>PP0+DRAM</t>
-  </si>
-  <si>
-    <t>Data Ratio</t>
-  </si>
-  <si>
-    <t>ours</t>
-  </si>
-  <si>
-    <t>baseline</t>
-  </si>
-  <si>
-    <t>diff</t>
-  </si>
-  <si>
-    <t>回归模型</t>
-  </si>
-  <si>
-    <t>分类模型</t>
+    <t>F1 of S</t>
   </si>
   <si>
     <t>完整</t>
@@ -164,21 +196,25 @@
   </si>
   <si>
     <t>分类模块和分类Loss换成CELoss</t>
+  </si>
+  <si>
+    <t>分类模块依赖Loss中的每个部分，尽管将整个分类模块替换形成的降低并不大，但在调整训练数据比例的实验中，当数据减少后，相比基线模型（使用linear和CELoss）性能提升由2%到10+%，同时，使用mlp带来的性能提升有限，综上所述，我们提出的分类模块对模型的性能提升具有明显效果，但由于数据过于充分，效果表现的不明显</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="#\ ?/?"/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="#\ ?/?"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,11 +223,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFAE81FF"/>
+      <name val="Droid Sans Mono"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -338,12 +393,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -671,152 +732,168 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1164,148 +1241,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="11.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.05555555555556" customWidth="1"/>
+    <col min="3" max="6" width="7.33333333333333" customWidth="1"/>
+    <col min="8" max="8" width="12.1666666666667"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="13" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>99.7666</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="6">
         <v>99.7662</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="6">
         <v>99.7666</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="6">
         <v>99.767</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="6"/>
+      <c r="G2" s="15">
+        <v>442344</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7">
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>98.286</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="6">
         <v>98.4008</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="6">
         <v>98.286</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="6">
         <v>98.69</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="6"/>
+      <c r="G3" s="15">
+        <v>442344</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>91.8696</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="15">
+        <v>442344</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>99.999</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="6">
         <v>99.999</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="6">
         <v>99.999</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="6">
         <v>99.999</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6"/>
+      <c r="G5">
+        <v>20488</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6">
         <v>100</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="6">
         <v>100</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="6">
         <v>100</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="6"/>
+      <c r="G6">
+        <v>20488</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
       <c r="B7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>99.999</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="6">
         <v>99.999</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="6">
         <v>99.999</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="6">
         <v>99.999</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="G7">
+        <v>20488</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
         <v>99.9868</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8">
+        <v>12128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="6" cm="1">
+        <f t="array" ref="C9">SUM(C2:C8*G2:G8)/SUM(G2:G8)</f>
+        <v>96.8170933606735</v>
+      </c>
+      <c r="D9" s="6" cm="1">
+        <f t="array" ref="D9">(SUM(D2:D3*G2:G3)+SUM(D5:D7*G5:G7))/(SUM(G2:G3)+SUM(G5:G7))</f>
+        <v>99.1429944364119</v>
+      </c>
+      <c r="E9" s="6" cm="1">
+        <f t="array" ref="E9">(SUM(E2:E3*G2:G3)+SUM(E5:E7*G5:G7))/(SUM(G2:G3)+SUM(G5:G7))</f>
+        <v>99.0895102672721</v>
+      </c>
+      <c r="F9" s="6" cm="1">
+        <f t="array" ref="F9">(SUM(F2:F3*G2:G3)+SUM(F5:F7*G5:G7))/(SUM(G2:G3)+SUM(G5:G7))</f>
+        <v>99.2785749351056</v>
+      </c>
+    </row>
+    <row r="11" spans="6:7">
+      <c r="F11" s="2"/>
+      <c r="G11" s="15"/>
+    </row>
+    <row r="12" spans="6:6">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="15" spans="3:4">
+      <c r="C15" s="2"/>
+      <c r="D15" s="15"/>
+    </row>
+    <row r="16" spans="3:4">
+      <c r="C16" s="2"/>
+      <c r="D16" s="15"/>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="2"/>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="2"/>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
   </mergeCells>
@@ -1321,25 +1471,25 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="11" t="s">
         <v>17</v>
       </c>
+      <c r="F1" s="11" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="7" t="s">
-        <v>18</v>
+      <c r="A2" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="B2">
         <v>99.977</v>
@@ -1358,8 +1508,8 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="7" t="s">
-        <v>19</v>
+      <c r="A3" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="B3">
         <v>99.471</v>
@@ -1378,8 +1528,8 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="7" t="s">
-        <v>20</v>
+      <c r="A4" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="B4">
         <v>0.506</v>
@@ -1410,25 +1560,25 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="11" t="s">
         <v>17</v>
       </c>
+      <c r="F1" s="11" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="7" t="s">
-        <v>18</v>
+      <c r="A2" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="B2">
         <v>94.35</v>
@@ -1447,8 +1597,8 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="7" t="s">
-        <v>19</v>
+      <c r="A3" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="B3">
         <v>90.808</v>
@@ -1467,8 +1617,8 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="7" t="s">
-        <v>20</v>
+      <c r="A4" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="B4">
         <v>3.54199999999999</v>
@@ -1495,75 +1645,85 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="2:6">
+      <c r="B1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>99.379</v>
+      </c>
+      <c r="C2">
+        <v>99.833</v>
+      </c>
+      <c r="D2">
+        <v>99.277</v>
+      </c>
+      <c r="E2" s="12">
+        <v>97.991</v>
+      </c>
+      <c r="F2">
+        <v>99.931</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>95.506</v>
+      </c>
+      <c r="C3">
+        <v>97.899</v>
+      </c>
+      <c r="D3">
+        <v>97.336</v>
+      </c>
+      <c r="E3">
+        <v>99.178</v>
+      </c>
+      <c r="F3">
+        <v>97.771</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2">
-        <v>79.427</v>
-      </c>
-      <c r="C2">
-        <v>81.733</v>
-      </c>
-      <c r="D2">
-        <v>84.992</v>
-      </c>
-      <c r="E2">
-        <v>95.97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3">
-        <v>62.172</v>
-      </c>
-      <c r="C3">
-        <v>71.545</v>
-      </c>
-      <c r="D3">
-        <v>81.32</v>
-      </c>
-      <c r="E3">
-        <v>87.731</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="B4">
-        <v>17.255</v>
+        <v>3.873</v>
       </c>
       <c r="C4">
-        <v>10.188</v>
+        <v>1.934</v>
       </c>
       <c r="D4">
-        <v>3.67200000000001</v>
+        <v>1.941</v>
       </c>
       <c r="E4">
-        <v>8.239</v>
+        <f>E2-E3</f>
+        <v>-1.187</v>
+      </c>
+      <c r="F4">
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>
@@ -1575,77 +1735,125 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="6" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="2:4">
-      <c r="B1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="7" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2">
-        <v>95.212</v>
-      </c>
-      <c r="C2">
-        <v>95.679</v>
-      </c>
-      <c r="D2">
-        <v>-0.466999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3">
-        <v>98.498</v>
-      </c>
-      <c r="C3">
-        <v>96.949</v>
-      </c>
-      <c r="D3">
-        <v>1.54900000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="7" t="s">
+      <c r="E1" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B4">
-        <v>98.627</v>
-      </c>
-      <c r="C4">
-        <v>96.944</v>
-      </c>
-      <c r="D4">
-        <v>1.68299999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="7" t="s">
+      <c r="B2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B5">
-        <v>99.904</v>
-      </c>
-      <c r="C5">
-        <v>98.793</v>
-      </c>
-      <c r="D5">
-        <v>1.11099999999999</v>
+      <c r="C2" s="6">
+        <v>79.427</v>
+      </c>
+      <c r="D2" s="6">
+        <v>62.172</v>
+      </c>
+      <c r="E2" s="6">
+        <v>17.255</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7"/>
+      <c r="B3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="6">
+        <v>81.733</v>
+      </c>
+      <c r="D3" s="6">
+        <v>71.545</v>
+      </c>
+      <c r="E3" s="6">
+        <v>10.188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7"/>
+      <c r="B4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="6">
+        <v>95.97</v>
+      </c>
+      <c r="D4" s="6">
+        <v>87.731</v>
+      </c>
+      <c r="E4" s="6">
+        <v>8.239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="6">
+        <v>97.469</v>
+      </c>
+      <c r="D5" s="6">
+        <v>92.451</v>
+      </c>
+      <c r="E5" s="6">
+        <v>5.018</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7"/>
+      <c r="B6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="6">
+        <v>98.388</v>
+      </c>
+      <c r="D6" s="6">
+        <v>95.792</v>
+      </c>
+      <c r="E6" s="6">
+        <v>2.596</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7"/>
+      <c r="B7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="6">
+        <v>99.931</v>
+      </c>
+      <c r="D7" s="6">
+        <v>97.771</v>
+      </c>
+      <c r="E7" s="6">
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1654,78 +1862,144 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelRow="6"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2">
-        <v>97.469</v>
-      </c>
-      <c r="C2">
-        <v>98.388</v>
-      </c>
-      <c r="D2">
-        <v>98.508</v>
-      </c>
-      <c r="E2">
-        <v>99.931</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3">
-        <v>92.451</v>
-      </c>
-      <c r="C3">
-        <v>95.792</v>
-      </c>
-      <c r="D3">
-        <v>96.28</v>
-      </c>
-      <c r="E3">
-        <v>97.771</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4">
-        <v>5.018</v>
-      </c>
-      <c r="C4">
-        <v>2.596</v>
-      </c>
-      <c r="D4">
-        <v>2.22799999999999</v>
-      </c>
-      <c r="E4">
-        <v>2.16</v>
+      <c r="B2" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="6">
+        <v>83.156</v>
+      </c>
+      <c r="D2" s="6">
+        <v>81.8</v>
+      </c>
+      <c r="E2" s="6">
+        <f>C2-D2</f>
+        <v>1.35600000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="7"/>
+      <c r="B3" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="C3" s="6">
+        <v>86.308</v>
+      </c>
+      <c r="D3" s="6">
+        <v>83.801</v>
+      </c>
+      <c r="E3" s="6">
+        <f>C3-D3</f>
+        <v>2.507</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="7"/>
+      <c r="B4" s="9">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6">
+        <v>91.8696</v>
+      </c>
+      <c r="D4" s="6">
+        <v>83.314</v>
+      </c>
+      <c r="E4" s="6">
+        <f>C4-D4</f>
+        <v>8.55560000000001</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="C5" s="6">
+        <v>97.6522</v>
+      </c>
+      <c r="D5" s="10">
+        <v>88.0108</v>
+      </c>
+      <c r="E5" s="6">
+        <f>C5-D5</f>
+        <v>9.64139999999999</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7"/>
+      <c r="B6" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="C6" s="6">
+        <v>98.2672</v>
+      </c>
+      <c r="D6" s="10">
+        <v>87.697</v>
+      </c>
+      <c r="E6" s="6">
+        <f>C6-D6</f>
+        <v>10.5702</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7"/>
+      <c r="B7" s="9">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6">
+        <v>98.4008</v>
+      </c>
+      <c r="D7" s="10">
+        <v>97.538</v>
+      </c>
+      <c r="E7" s="6">
+        <f>C7-D7</f>
+        <v>0.862800000000007</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1734,54 +2008,138 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="6">
+        <v>87.008</v>
+      </c>
+      <c r="D2" s="6">
+        <v>80.6454</v>
+      </c>
+      <c r="E2" s="6">
+        <f>C2-D2</f>
+        <v>6.3626</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7"/>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="6">
+        <v>87.72</v>
+      </c>
+      <c r="D3" s="6">
+        <v>74.7626</v>
+      </c>
+      <c r="E3" s="6">
+        <f>C3-D3</f>
+        <v>12.9574</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7"/>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="6">
+        <v>91.8696</v>
+      </c>
+      <c r="D4" s="6">
+        <v>83.3144</v>
+      </c>
+      <c r="E4" s="6">
+        <f>C4-D4</f>
+        <v>8.5552</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="3">
-        <v>87.008</v>
-      </c>
-      <c r="C2" s="3">
-        <v>99.582</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="3">
-        <v>87.72</v>
-      </c>
-      <c r="C3" s="3">
-        <v>99.675</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="3">
-        <v>91.8696</v>
-      </c>
-      <c r="C4" s="3">
-        <v>99.7662</v>
-      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="6">
+        <v>98.0744</v>
+      </c>
+      <c r="D5" s="6">
+        <v>88.0274</v>
+      </c>
+      <c r="E5" s="6">
+        <f>C5-D5</f>
+        <v>10.047</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7"/>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="6">
+        <v>97.4264</v>
+      </c>
+      <c r="D6" s="6">
+        <v>86.558</v>
+      </c>
+      <c r="E6" s="6">
+        <f>C6-D6</f>
+        <v>10.8684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7"/>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="6">
+        <v>98.4008</v>
+      </c>
+      <c r="D7" s="6">
+        <v>97.538</v>
+      </c>
+      <c r="E7" s="6">
+        <f>C7-D7</f>
+        <v>0.862800000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1790,203 +2148,97 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="6"/>
+  <cols>
+    <col min="5" max="5" width="20.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="2:7">
-      <c r="B2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="B3" s="3">
-        <v>83.156</v>
-      </c>
-      <c r="C3" s="3">
-        <v>81.8</v>
-      </c>
-      <c r="D3" s="3">
-        <f>B3-C3</f>
-        <v>1.35600000000001</v>
-      </c>
-      <c r="E3" s="3">
-        <v>99.463</v>
-      </c>
-      <c r="F3" s="3">
-        <v>97.19</v>
-      </c>
-      <c r="G3" s="3">
-        <f>E3-F3</f>
-        <v>2.273</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="B4" s="3">
-        <v>86.308</v>
-      </c>
-      <c r="C4" s="3">
-        <v>83.801</v>
-      </c>
-      <c r="D4" s="3">
-        <f>B4-C4</f>
-        <v>2.507</v>
-      </c>
-      <c r="E4" s="3">
-        <v>99.776</v>
-      </c>
-      <c r="F4" s="3">
-        <v>97.704</v>
-      </c>
-      <c r="G4" s="3">
-        <f>E4-F4</f>
-        <v>2.072</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3">
-        <v>91.8696</v>
-      </c>
-      <c r="C5" s="3">
-        <v>83.314</v>
-      </c>
-      <c r="D5" s="3">
-        <f>B5-C5</f>
-        <v>8.55560000000001</v>
-      </c>
-      <c r="E5" s="3">
-        <v>99.7662</v>
-      </c>
-      <c r="F5" s="3">
-        <v>99.486</v>
-      </c>
-      <c r="G5" s="3">
-        <f>E5-F5</f>
-        <v>0.280199999999994</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelRow="5" outlineLevelCol="6"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="2"/>
+        <v>38</v>
+      </c>
     </row>
     <row r="2" spans="2:4">
       <c r="B2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="3">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2">
         <v>91.8696</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="3">
-        <v>99.7666</v>
-      </c>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" ht="33.6" spans="1:7">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="3">
+        <v>41</v>
+      </c>
+      <c r="D3" s="2">
+        <v>98.4008</v>
+      </c>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" ht="33.6" customHeight="1" spans="1:7">
+      <c r="A4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="2">
         <v>83.3144</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="3">
-        <v>97.4934</v>
-      </c>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" ht="33.6" spans="1:4">
+        <v>43</v>
+      </c>
+      <c r="D4">
+        <v>84.1416</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" ht="33.6" customHeight="1" spans="1:4">
       <c r="A5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="3">
+        <v>44</v>
+      </c>
+      <c r="B5" s="2">
         <v>82.4528</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="3">
-        <v>99.486</v>
+      <c r="C5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5">
+        <v>97.538</v>
       </c>
     </row>
     <row r="6" spans="3:4">
       <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="3">
-        <v>99.4142</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D6" s="4">
+        <v>98.0008</v>
+      </c>
+    </row>
+    <row r="7" ht="308.4" customHeight="1" spans="4:4">
+      <c r="D7" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
